--- a/SwissTechSaqib/Swiss Tech Files 2025/Sales Reports 2025/Sales Report May-2026.xlsx
+++ b/SwissTechSaqib/Swiss Tech Files 2025/Sales Reports 2025/Sales Report May-2026.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dell5300\Documents\Swiss Tech Files 2025\Sales Reports 2025\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\SwissTechSaqib\Swiss Tech Files 2025\Sales Reports 2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{281D7AB8-2555-4C7C-A280-7406C1CFA19F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44055A3F-1E27-41DC-82EA-FDD723B12098}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{3DC8782F-D885-414F-8C55-534906B6F2AC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{3DC8782F-D885-414F-8C55-534906B6F2AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
